--- a/entorno/mir-v2/archivos_de_prueba/Chubut_con_errores/LEGAJO_NYA_2026_T1_Chubut_CON_ERRORES.xlsx
+++ b/entorno/mir-v2/archivos_de_prueba/Chubut_con_errores/LEGAJO_NYA_2026_T1_Chubut_CON_ERRORES.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="NyA" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Prov_Dto_Localidad" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="INSTRUCCIONES" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="LISTAS" sheetId="4" state="hidden" r:id="rId4"/>
-    <sheet name="ERRORES_ESPERADOS" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NyA" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prov_Dto_Localidad" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INSTRUCCIONES" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTAS" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ERRORES_ESPERADOS" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/entorno/mir-v2/archivos_de_prueba/Chubut_con_errores/LEGAJO_NYA_2026_T1_Chubut_CON_ERRORES.xlsx
+++ b/entorno/mir-v2/archivos_de_prueba/Chubut_con_errores/LEGAJO_NYA_2026_T1_Chubut_CON_ERRORES.xlsx
@@ -923,7 +923,7 @@
         </is>
       </c>
       <c r="U3" s="4" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
     </row>
     <row r="4">
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="U4" s="4" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
     </row>
     <row r="5">
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="U5" s="4" t="n">
-        <v>45934</v>
+        <v>45935</v>
       </c>
     </row>
     <row r="6">
@@ -1222,7 +1222,7 @@
         </is>
       </c>
       <c r="U6" s="4" t="n">
-        <v>45609</v>
+        <v>45610</v>
       </c>
     </row>
     <row r="7">
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="U7" s="4" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
     </row>
     <row r="8">
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="U8" s="4" t="n">
-        <v>45954</v>
+        <v>45955</v>
       </c>
     </row>
     <row r="9">
@@ -1521,7 +1521,7 @@
         </is>
       </c>
       <c r="U9" s="4" t="n">
-        <v>45628</v>
+        <v>45629</v>
       </c>
     </row>
     <row r="10">
@@ -1622,7 +1622,7 @@
         </is>
       </c>
       <c r="U10" s="4" t="n">
-        <v>45781</v>
+        <v>45782</v>
       </c>
     </row>
     <row r="11">
@@ -1719,7 +1719,7 @@
         </is>
       </c>
       <c r="U11" s="4" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
     </row>
     <row r="12">
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="U12" s="4" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
     </row>
     <row r="13">
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="U13" s="4" t="n">
-        <v>45734</v>
+        <v>45735</v>
       </c>
     </row>
     <row r="14">
@@ -2018,7 +2018,7 @@
         </is>
       </c>
       <c r="U14" s="4" t="n">
-        <v>46206</v>
+        <v>46207</v>
       </c>
     </row>
     <row r="15">
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="U15" s="4" t="n">
-        <v>46081</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="16">
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="U16" s="4" t="n">
-        <v>45684</v>
+        <v>45685</v>
       </c>
     </row>
     <row r="17">
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="U17" s="4" t="n">
-        <v>45601</v>
+        <v>45602</v>
       </c>
     </row>
     <row r="18">
@@ -2406,7 +2406,7 @@
         </is>
       </c>
       <c r="U18" s="4" t="n">
-        <v>45845</v>
+        <v>45846</v>
       </c>
     </row>
     <row r="19">
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="U19" s="4" t="n">
-        <v>45827</v>
+        <v>45828</v>
       </c>
     </row>
     <row r="20">
@@ -2604,7 +2604,7 @@
         </is>
       </c>
       <c r="U20" s="4" t="n">
-        <v>45870</v>
+        <v>45871</v>
       </c>
     </row>
     <row r="21">
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c r="U21" s="4" t="n">
-        <v>45788</v>
+        <v>45789</v>
       </c>
     </row>
     <row r="22">
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="U22" s="4" t="n">
-        <v>45743</v>
+        <v>45744</v>
       </c>
     </row>
     <row r="23">
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="U23" s="4" t="n">
-        <v>45652</v>
+        <v>45653</v>
       </c>
     </row>
     <row r="24">
@@ -3004,7 +3004,7 @@
         </is>
       </c>
       <c r="U24" s="4" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
     </row>
     <row r="25">
@@ -3101,7 +3101,7 @@
         </is>
       </c>
       <c r="U25" s="4" t="n">
-        <v>45838</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="26">
@@ -3202,7 +3202,7 @@
         </is>
       </c>
       <c r="U26" s="4" t="n">
-        <v>45720</v>
+        <v>45721</v>
       </c>
     </row>
     <row r="27">
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="U27" s="4" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
     </row>
     <row r="28">
@@ -3400,7 +3400,7 @@
         </is>
       </c>
       <c r="U28" s="4" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
     </row>
     <row r="29">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="U29" s="4" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
     </row>
     <row r="30">
@@ -3594,7 +3594,7 @@
         </is>
       </c>
       <c r="U30" s="4" t="n">
-        <v>45601</v>
+        <v>45602</v>
       </c>
     </row>
     <row r="31">
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="U31" s="4" t="n">
-        <v>46053</v>
+        <v>46054</v>
       </c>
     </row>
     <row r="32">
@@ -3788,7 +3788,7 @@
         </is>
       </c>
       <c r="U32" s="4" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="33">
@@ -3887,7 +3887,7 @@
         </is>
       </c>
       <c r="U33" s="4" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
     </row>
     <row r="34">
@@ -3990,7 +3990,7 @@
         </is>
       </c>
       <c r="U34" s="4" t="n">
-        <v>45606</v>
+        <v>45607</v>
       </c>
     </row>
     <row r="35">
@@ -4087,7 +4087,7 @@
         </is>
       </c>
       <c r="U35" s="4" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
     </row>
     <row r="36">
@@ -4187,7 +4187,7 @@
         </is>
       </c>
       <c r="U37" s="4" t="n">
-        <v>45665</v>
+        <v>45666</v>
       </c>
     </row>
     <row r="38">
@@ -4284,7 +4284,7 @@
         </is>
       </c>
       <c r="U38" s="4" t="n">
-        <v>45638</v>
+        <v>45639</v>
       </c>
     </row>
     <row r="39">
@@ -4381,7 +4381,7 @@
         </is>
       </c>
       <c r="U39" s="4" t="n">
-        <v>45820</v>
+        <v>45821</v>
       </c>
     </row>
     <row r="40">

--- a/entorno/mir-v2/archivos_de_prueba/Chubut_con_errores/LEGAJO_NYA_2026_T1_Chubut_CON_ERRORES.xlsx
+++ b/entorno/mir-v2/archivos_de_prueba/Chubut_con_errores/LEGAJO_NYA_2026_T1_Chubut_CON_ERRORES.xlsx
@@ -1,17 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NyA" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prov_Dto_Localidad" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INSTRUCCIONES" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTAS" sheetId="4" state="hidden" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ERRORES_ESPERADOS" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="NyA" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Prov_Dto_Localidad" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet name="Listas" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet name="ERRORES_ESPERADOS" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,10 +36,6 @@
     </font>
     <font>
       <b val="1"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="12"/>
     </font>
   </fonts>
   <fills count="5">
@@ -92,7 +87,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -103,10 +98,6 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -186,182 +177,171 @@
 <file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>RUNAC</author>
+    <author>MIR</author>
   </authors>
   <commentList>
     <comment ref="A2" authorId="0" shapeId="0">
       <text>
-        <t>ID del Niño, niña o Adolescente
-Identificador que le asigna el sistema provincial al niño, niña o adolescente. Es la clave con la que las nóminas (MPE, MPI, MPJ) se enganchan a este legajo.
-Qué se espera: un número entero
-Campo obligatorio.</t>
+        <t>ID del niño, niña o adolescente
+Obligatorio
+Qué va: Número entero.
+Identificador que le asigna el sistema provincial al niño, niña o adolescente. Es la clave con la que las nóminas (MPE, MPI, MPJ) se enganchan a este legajo.</t>
       </text>
     </comment>
     <comment ref="B2" authorId="0" shapeId="0">
       <text>
         <t>Apellido/s
-Qué se espera: texto
-Máximo 120 caracteres.
-Campo obligatorio.</t>
+Obligatorio
+Qué va: Texto, hasta 120 caracteres.</t>
       </text>
     </comment>
     <comment ref="C2" authorId="0" shapeId="0">
       <text>
         <t>Nombre/s
-Qué se espera: texto
-Máximo 120 caracteres.
-Campo obligatorio.</t>
+Obligatorio
+Qué va: Texto, hasta 120 caracteres.</t>
       </text>
     </comment>
     <comment ref="D2" authorId="0" shapeId="0">
       <text>
         <t>Tipo de documento de identidad
-Qué se espera: texto
-Máximo 26 caracteres.
-Elegir de la lista "Tipo de documento de identidad".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: DNI, Documento extranjero, Otro tipo de documentación, Sin documentación.</t>
       </text>
     </comment>
     <comment ref="E2" authorId="0" shapeId="0">
       <text>
         <t>Nº DNI
-Qué se espera: texto
-Máximo 15 caracteres.
-Campo obligatorio.</t>
+Obligatorio
+Qué va: Texto, hasta 15 caracteres.
+No se puede repetir en la hoja.</t>
       </text>
     </comment>
     <comment ref="F2" authorId="0" shapeId="0">
       <text>
         <t>Nº de CUIL
-Qué se espera: texto
-Máximo 13 caracteres.
-Campo obligatorio.</t>
+Obligatorio
+Qué va: Texto, hasta 13 caracteres.
+Tiene que ser un CUIL válido: se controla el dígito verificador.
+Aviso: Con el formato NN-NNNNNNNN-N.</t>
       </text>
     </comment>
     <comment ref="G2" authorId="0" shapeId="0">
       <text>
         <t>Otro núero de documentación de identidad (si no cuenta con DNI)
-Qué se espera: texto
-Máximo 15 caracteres.
-Campo obligatorio.</t>
+Obligatorio
+Qué va: Texto, hasta 15 caracteres.
+No se puede repetir en la hoja.</t>
       </text>
     </comment>
     <comment ref="H2" authorId="0" shapeId="0">
       <text>
         <t>Género
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Género".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Masculino, Femenino, Otros.</t>
       </text>
     </comment>
     <comment ref="I2" authorId="0" shapeId="0">
       <text>
         <t>País de nacimiento
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "País de nacimiento (legajo)".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: 11 opciones, en el desplegable.</t>
       </text>
     </comment>
     <comment ref="J2" authorId="0" shapeId="0">
       <text>
         <t>Fecha de nacimiento
-Qué se espera: una fecha, con formato dd/mm/aaaa
-Campo obligatorio.</t>
+Obligatorio
+Qué va: Fecha, como día/mes/año.
+Aviso: No puede ser posterior a hoy.</t>
       </text>
     </comment>
     <comment ref="K2" authorId="0" shapeId="0">
       <text>
         <t>Domicilio actual
-Qué se espera: texto
-Máximo 255 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 255 caracteres.</t>
       </text>
     </comment>
     <comment ref="L2" authorId="0" shapeId="0">
       <text>
         <t>Provincia
-Qué se espera: texto
-Máximo 120 caracteres.
-Elegir de la lista "Provincia (nomenclador oficial)".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.</t>
       </text>
     </comment>
     <comment ref="M2" authorId="0" shapeId="0">
       <text>
         <t>Departamento
-Qué se espera: texto
-Elegir de la lista "Departamento (nomenclador oficial)".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Aviso: No puede ser posterior a hoy.</t>
       </text>
     </comment>
     <comment ref="N2" authorId="0" shapeId="0">
       <text>
         <t>Localidad
-Qué se espera: texto
-Máximo 120 caracteres.
-Elegir de la lista "Localidad (lista de la jurisdicción)".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.</t>
       </text>
     </comment>
     <comment ref="O2" authorId="0" shapeId="0">
       <text>
         <t>¿Pertenece a pueblo originario? (o se identifica con algún pueblo originario?)
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "¿Presenta alguna discapacidad?".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: No, Sin datos, Sí.</t>
       </text>
     </comment>
     <comment ref="P2" authorId="0" shapeId="0">
       <text>
         <t>Pueblo originario (especificar)
-Qué se espera: texto
-No es obligatorio.</t>
+Obligatorio según otro dato
+Qué va: Texto.
+Obligatorio si «¿Pertenece a pueblo originario? (o se identifica con algún pueblo originario?)» es «Sí».</t>
       </text>
     </comment>
     <comment ref="Q2" authorId="0" shapeId="0">
       <text>
         <t>¿Presenta algún tipo de discapacidad?
-Qué se espera: texto
-Máximo 24 caracteres.
-Elegir de la lista "Discapacidad (legajo)".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: No presenta discapacidad, Visual, Auditiva, Mental, Motora, Visceral, Otros, Sin dato.</t>
       </text>
     </comment>
     <comment ref="R2" authorId="0" shapeId="0">
       <text>
         <t>¿Posee CUD?
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "¿Posee CUD?".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, En trámite, Vencido, No aplica, Sin datos.</t>
       </text>
     </comment>
     <comment ref="S2" authorId="0" shapeId="0">
       <text>
         <t>Cobertura salud
-Qué se espera: texto
-Máximo 22 caracteres.
-Elegir de la lista "Cobertura salud (legajo)".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Pública exclusivamente, Obra Social, Prepaga, Otra cobertura, Sin datos.</t>
       </text>
     </comment>
     <comment ref="T2" authorId="0" shapeId="0">
       <text>
         <t>¿Tiene hijos/as?
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "¿Presenta alguna discapacidad?".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: No, Sin datos, Sí.</t>
       </text>
     </comment>
     <comment ref="U2" authorId="0" shapeId="0">
       <text>
         <t>Fecha de actualización
-Qué se espera: una fecha, con formato dd/mm/aaaa
-No es obligatorio.</t>
+Opcional
+Qué va: Fecha, como día/mes/año.
+Aviso: No puede ser posterior a hoy.</t>
       </text>
     </comment>
   </commentList>
@@ -371,31 +351,28 @@
 <file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>RUNAC</author>
+    <author>MIR</author>
   </authors>
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
         <t>PROVINCIA
-Qué se espera: texto
-Máximo 120 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 120 caracteres.</t>
       </text>
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
         <t>DEPTO
-Qué se espera: texto
-Máximo 255 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 255 caracteres.</t>
       </text>
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
         <t>LOCALIDAD
-Qué se espera: texto
-Máximo 120 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 120 caracteres.</t>
       </text>
     </comment>
   </commentList>
@@ -721,7 +698,7 @@
     <row r="2" ht="48" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>ID del Niño, niña o Adolescente *</t>
+          <t>ID del niño, niña o adolescente *</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
@@ -846,7 +823,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>90000137</t>
+          <t>90000172</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -856,25 +833,25 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>90000137</t>
+          <t>90000168</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="J3" s="4" t="n">
-        <v>41182</v>
+        <v>40598</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Belgrano 1243</t>
+          <t>Alberdi 4567</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -889,41 +866,41 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Lago Puelo</t>
+          <t>Trelew</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Mapuche</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>No presenta discapacidad</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Obra Social</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Nota de ejemplo 1</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Visual</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>No aplica</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>Otra cobertura</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="U3" s="4" t="n">
-        <v>46257</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="4">
@@ -932,12 +909,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Fernández</t>
+          <t>Ledesma</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Mateo</t>
+          <t>Ana</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -947,7 +924,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>90000274</t>
+          <t>90000357</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -957,7 +934,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>90000274</t>
+          <t>90000363</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -967,15 +944,15 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="J4" s="4" t="n">
-        <v>40287</v>
+        <v>41081</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Sarmiento 1728</t>
+          <t>Mitre 4927</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -990,19 +967,15 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Lago Puelo</t>
+          <t>Esquel</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Nota de ejemplo 2</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr">
         <is>
           <t>Otros</t>
@@ -1010,21 +983,21 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
+          <t>En trámite</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Prepaga</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>Otra cobertura</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
       <c r="U4" s="4" t="n">
-        <v>46003</v>
+        <v>46071</v>
       </c>
     </row>
     <row r="5">
@@ -1038,7 +1011,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Lorenzo</t>
+          <t>Thiago</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1048,7 +1021,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>90000411</t>
+          <t>90000422</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1058,7 +1031,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>90000411</t>
+          <t>90000459</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1068,15 +1041,15 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Venezuela</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="J5" s="4" t="n">
-        <v>41572</v>
+        <v>41587</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Rivadavia 1373</t>
+          <t>Sarmiento 2266</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1091,37 +1064,41 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Puerto Madryn</t>
+          <t>El Hoyo</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 3</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Sin dato</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Pública exclusivamente</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Visual</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>Vencido</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>Pública exclusivamente</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
       <c r="U5" s="4" t="n">
-        <v>45935</v>
+        <v>46211</v>
       </c>
     </row>
     <row r="6">
@@ -1130,7 +1107,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ledesma</t>
+          <t>Quiroga</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1140,12 +1117,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>Otro tipo de documentación</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>90000548</t>
+          <t>90000621</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1155,7 +1132,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>90000548</t>
+          <t>90000572</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1165,15 +1142,15 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="J6" s="4" t="n">
-        <v>42375</v>
+        <v>40366</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>San Martín 3200</t>
+          <t>Alberdi 1966</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1188,41 +1165,37 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Trelew</t>
+          <t>El Hoyo</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Mental</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Qom</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>Mental</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Otra cobertura</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
         <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>Pública exclusivamente</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="U6" s="4" t="n">
-        <v>45610</v>
+        <v>45827</v>
       </c>
     </row>
     <row r="7">
@@ -1231,12 +1204,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Martínez</t>
+          <t>Villalba</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Isabella</t>
+          <t>Lorenzo</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1246,7 +1219,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>90000685</t>
+          <t>90000705</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1256,12 +1229,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>90000685</t>
+          <t>90000732</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1270,11 +1243,11 @@
         </is>
       </c>
       <c r="J7" s="4" t="n">
-        <v>40592</v>
+        <v>41272</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Mitre 2377</t>
+          <t>Alberdi 684</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1289,7 +1262,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Dolavon</t>
+          <t>Trevelin</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1304,26 +1277,26 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Visceral</t>
+          <t>Auditiva</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>En trámite</t>
+          <t>Vencido</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>Obra Social</t>
+          <t>Otra cobertura</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="U7" s="4" t="n">
-        <v>46014</v>
+        <v>45636</v>
       </c>
     </row>
     <row r="8">
@@ -1337,17 +1310,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Renata</t>
+          <t>Martina</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>Documento extranjero</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>90000822</t>
+          <t>90000909</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1357,25 +1330,25 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>90000822</t>
+          <t>90000863</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="J8" s="4" t="n">
-        <v>40879</v>
+        <v>40310</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Sarmiento 2105</t>
+          <t>Güemes 2684</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1390,7 +1363,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Comodoro Rivadavia</t>
+          <t>Gaiman</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1401,17 +1374,17 @@
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Motora</t>
+          <t>Mental</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No aplica</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Prepaga</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -1420,7 +1393,7 @@
         </is>
       </c>
       <c r="U8" s="4" t="n">
-        <v>45955</v>
+        <v>45620</v>
       </c>
     </row>
     <row r="9">
@@ -1429,22 +1402,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Paz</t>
+          <t>Díaz</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Isabella</t>
+          <t>Camila</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>Sin documentación</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>90000959</t>
+          <t>90000977</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1454,7 +1427,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>90000959</t>
+          <t>90000992</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1464,15 +1437,15 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="J9" s="4" t="n">
-        <v>41471</v>
+        <v>42478</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Mitre 2293</t>
+          <t>Sarmiento 2252</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1487,41 +1460,41 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Trelew</t>
+          <t>Lago Puelo</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Mapuche-Tehuelche</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Visceral</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Nota de ejemplo 7</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>Visceral</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>Otra cobertura</t>
+          <t>Obra Social</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="U9" s="4" t="n">
-        <v>45629</v>
+        <v>45786</v>
       </c>
     </row>
     <row r="10">
@@ -1530,22 +1503,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Díaz</t>
+          <t>Fernández</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sofía</t>
+          <t>Isabella</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Otro tipo de documentación</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>90001096</t>
+          <t>90001110</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1555,25 +1528,25 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>90001096</t>
+          <t>90001115</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="J10" s="4" t="n">
-        <v>42478</v>
+        <v>41908</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Sarmiento 2252</t>
+          <t>Sarmiento 620</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1588,41 +1561,41 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Lago Puelo</t>
+          <t>Gaiman</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 8</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Sin dato</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Prepaga</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Mapuche-Tehuelche</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>Visceral</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>Obra Social</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
       <c r="U10" s="4" t="n">
-        <v>45782</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="11">
@@ -1631,12 +1604,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Fernández</t>
+          <t>Villalba</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Isabella</t>
+          <t>Bautista</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1646,7 +1619,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>90001233</t>
+          <t>90001320</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1656,25 +1629,25 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>90001233</t>
+          <t>90001301</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="J11" s="4" t="n">
-        <v>40834</v>
+        <v>41572</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Güemes 3558</t>
+          <t>San Martín 2504</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1689,7 +1662,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Trevelin</t>
+          <t>Gaiman</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1700,17 +1673,17 @@
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>No presenta discapacidad</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>No aplica</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>Otra cobertura</t>
+          <t>Prepaga</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -1719,7 +1692,7 @@
         </is>
       </c>
       <c r="U11" s="4" t="n">
-        <v>46030</v>
+        <v>46109</v>
       </c>
     </row>
     <row r="12">
@@ -1733,7 +1706,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lorenzo</t>
+          <t>Renata</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1743,7 +1716,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>90001370</t>
+          <t>90001450</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1753,7 +1726,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>90001370</t>
+          <t>90001408</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1763,15 +1736,15 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Perú</t>
         </is>
       </c>
       <c r="J12" s="4" t="n">
-        <v>42378</v>
+        <v>42673</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Güemes 2285</t>
+          <t>Belgrano 1352</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1786,32 +1759,32 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>El Hoyo</t>
+          <t>Sarmiento</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Mapuche</t>
+          <t>Nota de ejemplo 10</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Motora</t>
+          <t>No presenta discapacidad</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Vencido</t>
+          <t>No aplica</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>Obra Social</t>
+          <t>Prepaga</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -1820,7 +1793,7 @@
         </is>
       </c>
       <c r="U12" s="4" t="n">
-        <v>46284</v>
+        <v>46272</v>
       </c>
     </row>
     <row r="13">
@@ -1829,7 +1802,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cabrera</t>
+          <t>Fernández</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1844,7 +1817,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>90001507</t>
+          <t>90001546</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1854,25 +1827,25 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>90001507</t>
+          <t>90001537</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="J13" s="4" t="n">
-        <v>42258</v>
+        <v>42502</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>San Martín 2544</t>
+          <t>San Martín 801</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1887,41 +1860,37 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Camarones</t>
+          <t>Lago Puelo</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Auditiva</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Otra cobertura</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Nota de ejemplo 11</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>Mental</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>Prepaga</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="U13" s="4" t="n">
-        <v>45735</v>
+        <v>46122</v>
       </c>
     </row>
     <row r="14">
@@ -1930,22 +1899,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ojeda</t>
+          <t>Rodríguez</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Renata</t>
+          <t>Martina</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>Sin documentación</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>90001644</t>
+          <t>90001671</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1955,7 +1924,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>90001644</t>
+          <t>90001713</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1965,15 +1934,15 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="J14" s="4" t="n">
-        <v>42180</v>
+        <v>41455</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>San Martín 1016</t>
+          <t>Mitre 3159</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1988,37 +1957,41 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Río Mayo</t>
+          <t>Dolavon</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Mapuche</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Mental</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>Pública exclusivamente</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>Mental</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>Obra Social</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
       <c r="U14" s="4" t="n">
-        <v>46207</v>
+        <v>46270</v>
       </c>
     </row>
     <row r="15">
@@ -2027,22 +2000,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fernández</t>
+          <t>Ledesma</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bautista</t>
+          <t>Martina</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Sin documentación</t>
+          <t>Documento extranjero</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>90001781</t>
+          <t>90001856</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2052,7 +2025,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>90001781</t>
+          <t>90001809</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2062,15 +2035,15 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Perú</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="J15" s="4" t="n">
-        <v>40694</v>
+        <v>40420</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Belgrano 3993</t>
+          <t>Belgrano 652</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2085,7 +2058,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Rada Tilly</t>
+          <t>Río Mayo</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -2096,26 +2069,26 @@
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Visual</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No aplica</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
+          <t>Obra Social</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
       <c r="U15" s="4" t="n">
-        <v>46082</v>
+        <v>45606</v>
       </c>
     </row>
     <row r="16">
@@ -2124,22 +2097,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cabrera</t>
+          <t>Díaz</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Valentina</t>
+          <t>Mateo</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Sin documentación</t>
+          <t>Documento extranjero</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>90001918</t>
+          <t>90001991</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2149,25 +2122,25 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>90001918</t>
+          <t>90001991</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="J16" s="4" t="n">
-        <v>41708</v>
+        <v>42116</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Mitre 4339</t>
+          <t>Güemes 3434</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2182,7 +2155,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Dolavon</t>
+          <t>Puerto Madryn</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -2193,26 +2166,26 @@
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Mental</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>En trámite</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>Prepaga</t>
+          <t>Otra cobertura</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="U16" s="4" t="n">
-        <v>45685</v>
+        <v>45813</v>
       </c>
     </row>
     <row r="17">
@@ -2221,22 +2194,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Quiroga</t>
+          <t>Paz</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Mateo</t>
+          <t>Bautista</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Documento extranjero</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>90002055</t>
+          <t>90002141</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2246,12 +2219,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>90002055</t>
+          <t>90002138</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2260,11 +2233,11 @@
         </is>
       </c>
       <c r="J17" s="4" t="n">
-        <v>40420</v>
+        <v>40427</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Belgrano 652</t>
+          <t>Mitre 2879</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2279,7 +2252,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Río Mayo</t>
+          <t>El Hoyo</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2290,17 +2263,17 @@
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Visual</t>
+          <t>Mental</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>No aplica</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>Obra Social</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
@@ -2309,7 +2282,7 @@
         </is>
       </c>
       <c r="U17" s="4" t="n">
-        <v>45602</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="18">
@@ -2318,22 +2291,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Díaz</t>
+          <t>Romero</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Mateo</t>
+          <t>Sofía</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Documento extranjero</t>
+          <t>Otro tipo de documentación</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>90002192</t>
+          <t>90002251</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2343,25 +2316,25 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>90002192</t>
+          <t>90002223</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="J18" s="4" t="n">
-        <v>42539</v>
+        <v>42433</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Mitre 2090</t>
+          <t>San Martín 514</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2376,37 +2349,41 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>El Hoyo</t>
+          <t>El Maitén</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Mapuche</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Mental</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Otra cobertura</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>Mental</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>Pública exclusivamente</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
       <c r="U18" s="4" t="n">
-        <v>45846</v>
+        <v>45799</v>
       </c>
     </row>
     <row r="19">
@@ -2415,12 +2392,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sosa</t>
+          <t>Martínez</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Camila</t>
+          <t>Lorenzo</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2430,7 +2407,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>90002329</t>
+          <t>90002336</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2440,7 +2417,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>90002329</t>
+          <t>90002350</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2454,11 +2431,11 @@
         </is>
       </c>
       <c r="J19" s="4" t="n">
-        <v>40582</v>
+        <v>41778</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>San Martín 3398</t>
+          <t>Rivadavia 3827</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2473,7 +2450,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Lago Puelo</t>
+          <t>Esquel</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2481,10 +2458,14 @@
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 17</t>
+        </is>
+      </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Mental</t>
+          <t>Sin dato</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2499,11 +2480,11 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="U19" s="4" t="n">
-        <v>45828</v>
+        <v>46069</v>
       </c>
     </row>
     <row r="20">
@@ -2512,22 +2493,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>López</t>
+          <t>Gómez</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Camila</t>
+          <t>Joaquín</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Documento extranjero</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>90002466</t>
+          <t>90002506</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2537,25 +2518,25 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>90002466</t>
+          <t>90002473</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="J20" s="4" t="n">
-        <v>41202</v>
+        <v>42131</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Güemes 717</t>
+          <t>Sarmiento 4450</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2570,41 +2551,41 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Dolavon</t>
+          <t>Comodoro Rivadavia</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 18</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Visual</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Pública exclusivamente</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Mapuche</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>No presenta discapacidad</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>Obra Social</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="U20" s="4" t="n">
-        <v>45871</v>
+        <v>46222</v>
       </c>
     </row>
     <row r="21">
@@ -2613,12 +2594,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Díaz</t>
+          <t>Villalba</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Benjamín</t>
+          <t>Lorenzo</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2628,7 +2609,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>90002603</t>
+          <t>90002654</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2638,25 +2619,25 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>90002603</t>
+          <t>90002618</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="J21" s="4" t="n">
-        <v>40853</v>
+        <v>42550</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Mitre 117</t>
+          <t>Sarmiento 425</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2671,28 +2652,28 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Gaiman</t>
+          <t>Trevelin</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Motora</t>
+          <t>Visceral</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>Vencido</t>
+          <t>En trámite</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Obra Social</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
@@ -2701,7 +2682,7 @@
         </is>
       </c>
       <c r="U21" s="4" t="n">
-        <v>45789</v>
+        <v>45970</v>
       </c>
     </row>
     <row r="22">
@@ -2710,22 +2691,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>López</t>
+          <t>Martínez</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Mateo</t>
+          <t>Valentina</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Otro tipo de documentación</t>
+          <t>Sin documentación</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>90002740</t>
+          <t>90002756</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2735,25 +2716,25 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>90002740</t>
+          <t>90002825</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="J22" s="4" t="n">
-        <v>42551</v>
+        <v>42051</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Alberdi 4541</t>
+          <t>Rivadavia 694</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2773,36 +2754,36 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 20</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Visual</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Mapuche</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>No presenta discapacidad</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>No aplica</t>
-        </is>
-      </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>Otra cobertura</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="U22" s="4" t="n">
-        <v>45744</v>
+        <v>45773</v>
       </c>
     </row>
     <row r="23">
@@ -2811,22 +2792,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>López</t>
+          <t>Rodríguez</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ana</t>
+          <t>Sofía</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>Otro tipo de documentación</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>90002877</t>
+          <t>90002885</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2836,25 +2817,25 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>90002877</t>
+          <t>90002908</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="J23" s="4" t="n">
-        <v>42616</v>
+        <v>40825</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>San Martín 2026</t>
+          <t>Mitre 4550</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2869,12 +2850,12 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Gaiman</t>
+          <t>Lago Puelo</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2884,12 +2865,12 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>Mental</t>
+          <t>No presenta discapacidad</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>No aplica</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2899,11 +2880,11 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="U23" s="4" t="n">
-        <v>45653</v>
+        <v>45612</v>
       </c>
     </row>
     <row r="24">
@@ -2917,17 +2898,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Camila</t>
+          <t>Renata</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Otro tipo de documentación</t>
+          <t>Documento extranjero</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>90003014</t>
+          <t>90003047</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2937,25 +2918,25 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>90003014</t>
+          <t>90003028</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Perú</t>
         </is>
       </c>
       <c r="J24" s="4" t="n">
-        <v>41465</v>
+        <v>40815</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Belgrano 2275</t>
+          <t>Rivadavia 2408</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2970,7 +2951,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Gaiman</t>
+          <t>Trevelin</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2985,12 +2966,12 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>Motora</t>
+          <t>Visceral</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>Vencido</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3000,11 +2981,11 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="U24" s="4" t="n">
-        <v>46278</v>
+        <v>45791</v>
       </c>
     </row>
     <row r="25">
@@ -3013,12 +2994,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Díaz</t>
+          <t>Rodríguez</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Joaquín</t>
+          <t>Renata</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3028,7 +3009,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>90003151</t>
+          <t>90003162</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3038,25 +3019,25 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>90003151</t>
+          <t>90003232</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Perú</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="J25" s="4" t="n">
-        <v>41052</v>
+        <v>40359</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Sarmiento 2272</t>
+          <t>San Martín 2832</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -3071,37 +3052,41 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Comodoro Rivadavia</t>
+          <t>El Hoyo</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 23</t>
+        </is>
+      </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>Mental</t>
+          <t>Motora</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>En trámite</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>Prepaga</t>
+          <t>Otra cobertura</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="U25" s="4" t="n">
-        <v>45839</v>
+        <v>45854</v>
       </c>
     </row>
     <row r="26">
@@ -3110,22 +3095,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Paz</t>
+          <t>Quiroga</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Martina</t>
+          <t>Ana</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Otro tipo de documentación</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>90003288</t>
+          <t>90003297</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3135,74 +3120,74 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>90003288</t>
+          <t>90003376</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
+          <t>Perú</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="n">
+        <v>40326</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Güemes 3124</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Chubut</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Dato 24</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Trevelin</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Mapuche-Tehuelche</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Auditiva</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>Prepaga</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="J26" s="4" t="n">
-        <v>42345</v>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>San Martín 4643</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>Dato 24</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>Esquel</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>Tehuelche</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>Motora</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>Pública exclusivamente</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
       <c r="U26" s="4" t="n">
-        <v>45721</v>
+        <v>46251</v>
       </c>
     </row>
     <row r="27">
@@ -3211,22 +3196,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>López</t>
+          <t>Sosa</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Valentina</t>
+          <t>Mateo</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Otro tipo de documentación</t>
+          <t>Documento extranjero</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>90003425</t>
+          <t>90003510</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3236,25 +3221,25 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>90003425</t>
+          <t>90003438</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Perú</t>
         </is>
       </c>
       <c r="J27" s="4" t="n">
-        <v>41583</v>
+        <v>41843</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Belgrano 2262</t>
+          <t>Sarmiento 1366</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -3269,37 +3254,37 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Rada Tilly</t>
+          <t>Río Mayo</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>No presenta discapacidad</t>
+          <t>Auditiva</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Vencido</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>Otra cobertura</t>
+          <t>Pública exclusivamente</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="U27" s="4" t="n">
-        <v>46242</v>
+        <v>45951</v>
       </c>
     </row>
     <row r="28">
@@ -3308,22 +3293,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Gómez</t>
+          <t>Ojeda</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Thiago</t>
+          <t>Renata</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Documento extranjero</t>
+          <t>Sin documentación</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>90003562</t>
+          <t>90003647</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3333,25 +3318,25 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>90003562</t>
+          <t>90003593</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="J28" s="4" t="n">
-        <v>40840</v>
+        <v>40621</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Alberdi 3719</t>
+          <t>Mitre 417</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3366,41 +3351,37 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Rada Tilly</t>
+          <t>Camarones</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>Mapuche</t>
-        </is>
-      </c>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>Visual</t>
+          <t>Mental</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Vencido</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>Obra Social</t>
+          <t>Prepaga</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="U28" s="4" t="n">
-        <v>46251</v>
+        <v>46058</v>
       </c>
     </row>
     <row r="29">
@@ -3409,12 +3390,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Paz</t>
+          <t>Martínez</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Thiago</t>
+          <t>Ana</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3424,7 +3405,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>90003699</t>
+          <t>90003750</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3434,7 +3415,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>90003699</t>
+          <t>90003741</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3444,15 +3425,15 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="J29" s="4" t="n">
-        <v>40350</v>
+        <v>41322</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Rivadavia 3087</t>
+          <t>Rivadavia 4273</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3467,37 +3448,41 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Río Mayo</t>
+          <t>Gaiman</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 27</t>
+        </is>
+      </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>Mental</t>
+          <t>Visceral</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>Pública exclusivamente</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>Obra Social</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
       <c r="U29" s="4" t="n">
-        <v>46182</v>
+        <v>46109</v>
       </c>
     </row>
     <row r="30">
@@ -3506,22 +3491,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Sosa</t>
+          <t>Ledesma</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Isabella</t>
+          <t>Valentina</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Sin documentación</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>90003836</t>
+          <t>90003849</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3531,25 +3516,25 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>90003836</t>
+          <t>90003912</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="J30" s="4" t="n">
-        <v>41148</v>
+        <v>41463</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Güemes 1431</t>
+          <t>Mitre 4289</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3564,37 +3549,41 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>El Hoyo</t>
+          <t>Trelew</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr"/>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 28</t>
+        </is>
+      </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>No presenta discapacidad</t>
+          <t>Mental</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>En trámite</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>Prepaga</t>
+          <t>Pública exclusivamente</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="U30" s="4" t="n">
-        <v>45602</v>
+        <v>45845</v>
       </c>
     </row>
     <row r="31">
@@ -3603,12 +3592,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Paz</t>
+          <t>Gómez</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bautista</t>
+          <t>Martina</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3618,7 +3607,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>90003973</t>
+          <t>90004019</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3628,25 +3617,25 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>90003973</t>
+          <t>90004028</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="J31" s="4" t="n">
-        <v>40621</v>
+        <v>41531</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Mitre 417</t>
+          <t>Sarmiento 2671</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3661,23 +3650,27 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Camarones</t>
+          <t>El Maitén</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 29</t>
+        </is>
+      </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>Mental</t>
+          <t>Motora</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>Vencido</t>
+          <t>No aplica</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3687,11 +3680,11 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="U31" s="4" t="n">
-        <v>46054</v>
+        <v>45873</v>
       </c>
     </row>
     <row r="32">
@@ -3700,22 +3693,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Martínez</t>
+          <t>Sosa</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ana</t>
+          <t>Camila</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Documento extranjero</t>
+          <t>Otro tipo de documentación</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>90004110</t>
+          <t>90004180</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3725,25 +3718,25 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>90004110</t>
+          <t>90004126</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="J32" s="4" t="n">
-        <v>41320</v>
+        <v>41731</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Güemes 668</t>
+          <t>Alberdi 1525</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3758,37 +3751,41 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>El Hoyo</t>
+          <t>Trevelin</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr"/>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Mapuche-Tehuelche</t>
+        </is>
+      </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>No presenta discapacidad</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>En trámite</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Prepaga</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="U32" s="4" t="n">
-        <v>46259</v>
+        <v>45851</v>
       </c>
     </row>
     <row r="33">
@@ -3797,12 +3794,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Fernández</t>
+          <t>Ojeda</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Renata</t>
+          <t>Joaquín</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3812,7 +3809,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>90136863</t>
+          <t>90136922</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3822,17 +3819,17 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>90136863</t>
+          <t>90136919</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -3842,7 +3839,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>San Martín 988</t>
+          <t>Sarmiento 3976</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3857,23 +3854,23 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Trevelin</t>
+          <t>El Hoyo</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>Visceral</t>
+          <t>Visual</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>Vencido</t>
+          <t>En trámite</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3887,7 +3884,7 @@
         </is>
       </c>
       <c r="U33" s="4" t="n">
-        <v>46169</v>
+        <v>45643</v>
       </c>
     </row>
     <row r="34">
@@ -3898,22 +3895,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Romero</t>
+          <t>Ledesma</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Renata</t>
+          <t>Thiago</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Documento extranjero</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>90136863</t>
+          <t>90136893</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -3923,7 +3920,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>90136863</t>
+          <t>90136949</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3933,15 +3930,15 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="J34" s="4" t="n">
-        <v>41965</v>
+        <v>40994</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>San Martín 4359</t>
+          <t>Belgrano 300</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3956,41 +3953,37 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Río Mayo</t>
+          <t>Rawson</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>Visual</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>Otra cobertura</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>Nota de ejemplo 999</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>Mental</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>En trámite</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>Otra cobertura</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="U34" s="4" t="n">
-        <v>45607</v>
+        <v>45702</v>
       </c>
     </row>
     <row r="35">
@@ -3999,12 +3992,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Sosa</t>
+          <t>Martínez</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Joaquín</t>
+          <t>Bautista</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4014,7 +4007,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>90136863</t>
+          <t>90136926</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4024,25 +4017,25 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>90136863</t>
+          <t>90136914</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="J35" s="4" t="n">
-        <v>41409</v>
+        <v>40201</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Sarmiento 2633</t>
+          <t>Güemes 973</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -4057,7 +4050,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>El Maitén</t>
+          <t>El Hoyo</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -4068,7 +4061,7 @@
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Auditiva</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -4078,16 +4071,16 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>Prepaga</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="U35" s="4" t="n">
-        <v>46157</v>
+        <v>46240</v>
       </c>
     </row>
     <row r="36">
@@ -4099,22 +4092,22 @@
       <c r="A37" s="3" t="n"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Martínez</t>
+          <t>Quiroga</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Camila</t>
+          <t>Mateo</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Sin documentación</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>90136863</t>
+          <t>90136921</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -4124,70 +4117,74 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>90136863</t>
+          <t>90136880</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="n">
+        <v>42354</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Sarmiento 4977</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Chubut</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Dato 999</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Sarmiento</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 999</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
           <t>Otros</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Brasil</t>
-        </is>
-      </c>
-      <c r="J37" s="4" t="n">
-        <v>42510</v>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>Rivadavia 3426</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>Dato 999</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>Rada Tilly</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>Otra cobertura</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>Motora</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>Otra cobertura</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
       <c r="U37" s="4" t="n">
-        <v>45666</v>
+        <v>45805</v>
       </c>
     </row>
     <row r="38">
@@ -4201,17 +4198,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Thiago</t>
+          <t>Valentina</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Sin documentación</t>
+          <t>Documento extranjero</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>90136863</t>
+          <t>90136944</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4221,12 +4218,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>90136863</t>
+          <t>90136898</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4235,11 +4232,11 @@
         </is>
       </c>
       <c r="J38" s="4" t="n">
-        <v>41054</v>
+        <v>41158</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Sarmiento 3976</t>
+          <t>Rivadavia 3703</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -4254,7 +4251,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>El Hoyo</t>
+          <t>Trelew</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -4265,7 +4262,7 @@
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>Visual</t>
+          <t>Mental</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -4275,16 +4272,16 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
+          <t>Prepaga</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
       <c r="U38" s="4" t="n">
-        <v>45639</v>
+        <v>45738</v>
       </c>
     </row>
     <row r="39">
@@ -4293,22 +4290,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ledesma</t>
+          <t>Fernández</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Thiago</t>
+          <t>Sofía</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>Documento extranjero</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>90000137</t>
+          <t>90000172</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4318,70 +4315,74 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>90136863</t>
+          <t>90136912</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="n">
+        <v>41055</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>San Martín 3498</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Chubut</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Dato 999</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Gaiman</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
           <t>Sin datos</t>
         </is>
       </c>
-      <c r="J39" s="4" t="n">
-        <v>41450</v>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>Belgrano 1731</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>Dato 999</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>Comodoro Rivadavia</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Nota de ejemplo 999</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>Sin dato</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>Vencido</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>Pública exclusivamente</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>Mental</t>
-        </is>
-      </c>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>Vencido</t>
-        </is>
-      </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="U39" s="4" t="n">
-        <v>45821</v>
+        <v>45861</v>
       </c>
     </row>
     <row r="40">
@@ -5202,28 +5203,28 @@
   </sheetData>
   <dataValidations count="8">
     <dataValidation sqref="D3:D202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Tipo de documento de identidad&quot;." type="list">
-      <formula1>LISTAS!$J$2:$J$5</formula1>
+      <formula1>Listas!$J$2:$J$5</formula1>
     </dataValidation>
     <dataValidation sqref="H3:H202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Género&quot;." type="list">
-      <formula1>LISTAS!$C$2:$C$4</formula1>
+      <formula1>Listas!$C$2:$C$4</formula1>
     </dataValidation>
     <dataValidation sqref="I3:I202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;País de nacimiento&quot;." type="list">
-      <formula1>LISTAS!$G$2:$G$12</formula1>
+      <formula1>Listas!$G$2:$G$12</formula1>
     </dataValidation>
     <dataValidation sqref="O3:O202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;¿Pertenece a pueblo originario? (o se identifica con algún pueblo originario?)&quot;." type="list">
-      <formula1>LISTAS!$I$2:$I$4</formula1>
+      <formula1>Listas!$I$2:$I$4</formula1>
     </dataValidation>
     <dataValidation sqref="Q3:Q202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;¿Presenta algún tipo de discapacidad?&quot;." type="list">
-      <formula1>LISTAS!$B$2:$B$9</formula1>
+      <formula1>Listas!$B$2:$B$9</formula1>
     </dataValidation>
     <dataValidation sqref="R3:R202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;¿Posee CUD?&quot;." type="list">
-      <formula1>LISTAS!$H$2:$H$7</formula1>
+      <formula1>Listas!$H$2:$H$7</formula1>
     </dataValidation>
     <dataValidation sqref="S3:S202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cobertura salud&quot;." type="list">
-      <formula1>LISTAS!$A$2:$A$6</formula1>
+      <formula1>Listas!$A$2:$A$6</formula1>
     </dataValidation>
     <dataValidation sqref="T3:T202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;¿Tiene hijos/as?&quot;." type="list">
-      <formula1>LISTAS!$I$2:$I$4</formula1>
+      <formula1>Listas!$I$2:$I$4</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5237,7 +5238,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5262,550 +5263,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Dato 1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Gaiman</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Dato 2</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Río Mayo</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Dato 3</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>El Maitén</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Dato 4</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Trevelin</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Dato 5</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Puerto Madryn</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Dato 6</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Lago Puelo</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Dato 7</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Lago Puelo</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Dato 8</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Gaiman</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Dato 9</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Dolavon</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Dato 10</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Gaiman</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Dato 11</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Puerto Madryn</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Dato 12</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Comodoro Rivadavia</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Dato 13</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>El Maitén</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Dato 14</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Lago Puelo</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Dato 15</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Rawson</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Dato 16</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Río Mayo</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Dato 17</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>El Hoyo</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Dato 18</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Camarones</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Dato 19</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>El Hoyo</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Dato 20</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Río Mayo</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Dato 21</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Trelew</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Dato 22</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>El Hoyo</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Dato 23</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Gaiman</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Dato 24</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Puerto Madryn</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Dato 25</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Comodoro Rivadavia</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Dato 26</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>El Hoyo</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Dato 27</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Lago Puelo</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Dato 28</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Rada Tilly</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Dato 29</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Dolavon</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Dato 30</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Rawson</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>XXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXXX</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Dato 999</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Rada Tilly</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Chubut</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Dato 999</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Puerto Madryn</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -5813,320 +5270,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B28"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="95" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>Campo</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>Indicación para el llenado</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>Hoja: NyA</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ID del Niño, niña o Adolescente</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>Identificador que le asigna el sistema provincial al niño, niña o adolescente. Es la clave con la que las nóminas (MPE, MPI, MPJ) se enganchan a este legajo.
-Campo obligatorio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Apellido/s</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Campo obligatorio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Nombre/s</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Campo obligatorio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Tipo de documento de identidad</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Tipo de documento de identidad".</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Nº DNI</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>Campo obligatorio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Nº de CUIL</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Campo obligatorio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Otro núero de documentación de identidad (si no cuenta con DNI)</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>Campo obligatorio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Género</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Género".</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>País de nacimiento</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "País de nacimiento (legajo)".</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fecha de nacimiento</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Campo obligatorio.
-Formato de fecha: dd/mm/aaaa.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Domicilio actual</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Provincia</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Provincia (nomenclador oficial)".</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Departamento (nomenclador oficial)".</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Localidad</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Localidad (lista de la jurisdicción)".</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>¿Pertenece a pueblo originario? (o se identifica con algún pueblo originario?)</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "¿Presenta alguna discapacidad?".</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Pueblo originario (especificar)</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>¿Presenta algún tipo de discapacidad?</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Discapacidad (legajo)".</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>¿Posee CUD?</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "¿Posee CUD?".</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Cobertura salud</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Cobertura salud (legajo)".</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>¿Tiene hijos/as?</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "¿Presenta alguna discapacidad?".</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Fecha de actualización</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Formato de fecha: dd/mm/aaaa.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>Hoja: Prov_Dto_Localidad</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>PROVINCIA</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>DEPTO</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>LOCALIDAD</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="n"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6426,13 +5569,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6472,50 +5615,175 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Prov_Dto_Localidad</t>
+          <t>NyA</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Fecha de nacimiento</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>fila_vacia_intercalada</t>
+          <t>fecha_invalida</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>una fila vacía en el medio de los datos</t>
+          <t>una fecha que no existe</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Prov_Dto_Localidad</t>
+          <t>NyA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>PROVINCIA</t>
+          <t>ID del niño, niña o adolescente</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>texto_en_numero</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>letras donde va un número</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NyA</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>35</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Tipo de documento de identidad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>valor_fuera_de_catalogo</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>un valor que no está en la lista</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NyA</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>36</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>fila_vacia_intercalada</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>una fila vacía en el medio de los datos</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NyA</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>37</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ID del niño, niña o adolescente</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>obligatorio_vacio</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>un campo obligatorio sin completar</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NyA</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>38</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Apellido/s</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>texto_muy_largo</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>un texto más largo de lo admitido</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NyA</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>39</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Nº DNI</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>documento_repetido</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>el mismo documento dos veces</t>
         </is>
       </c>
     </row>
